--- a/source/人工智能场景计划表-0820.xlsx
+++ b/source/人工智能场景计划表-0820.xlsx
@@ -1811,10 +1811,10 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="0" dbFileVersion="0" changeLogVersion="0">
-    <open main="41" threadCnt="1"/>
+    <open main="54" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="0" sheetStid="1">
-        <open main="2" threadCnt="1"/>
+        <open main="3" threadCnt="1"/>
       </sheetInfo>
     </sheetInfos>
   </bookInfo>
@@ -2285,7 +2285,7 @@
         <v>46256</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>26</v>
@@ -2759,7 +2759,7 @@
         <v>46386</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>26</v>
@@ -3133,7 +3133,7 @@
         <v>46285</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I29" s="12" t="s">
         <v>19</v>
